--- a/storage/app/public/templates/beregu.xlsx
+++ b/storage/app/public/templates/beregu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/radhifauzan/Desktop/side-projects/bowling-system-backend/storage/app/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2956629C-F13C-8747-8E5C-585F0EA4275C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A0A750-6D2B-3A4A-B267-CCECF9F2BC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
